--- a/docs/downloads/04/tbl_class_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_class_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -394,14 +394,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="E2">
-        <v>1.6</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="3">
@@ -417,14 +417,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D3">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>90.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4">
@@ -440,14 +440,8 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>7.9</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -509,14 +503,8 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>2.9</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -578,14 +566,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D10">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E10">
-        <v>9.5</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="11">
@@ -596,19 +584,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11">
-        <v>4.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
@@ -624,7 +612,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D12">
@@ -642,7 +630,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -651,10 +639,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="E13">
-        <v>50</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -670,7 +658,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D14">
@@ -683,12 +671,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6-10 ans</t>
+          <t>11-14 ans</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -697,10 +685,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="E15">
-        <v>90.90000000000001</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="16">
@@ -716,14 +704,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E16">
-        <v>1.6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
@@ -739,14 +727,8 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>49</v>
-      </c>
-      <c r="E17">
-        <v>80.3</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -757,19 +739,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11-14 ans</t>
+          <t>15-17 ans</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D18">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E18">
-        <v>18</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="19">
@@ -785,14 +767,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D19">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E19">
-        <v>47.4</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="20">
@@ -808,14 +790,8 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>6</v>
-      </c>
-      <c r="E20">
-        <v>31.6</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -826,19 +802,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15-17 ans</t>
+          <t>18-25 ans</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D21">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="E21">
-        <v>21.1</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="22">
@@ -854,14 +830,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D22">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E22">
-        <v>39.1</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="23">
@@ -877,14 +853,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D23">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E23">
-        <v>36.2</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="24">
@@ -895,19 +871,13 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>15</v>
-      </c>
-      <c r="E24">
-        <v>21.7</v>
+          <t>Primaire</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -918,19 +888,13 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>2</v>
-      </c>
-      <c r="E25">
-        <v>2.9</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -941,19 +905,13 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
           <t>Inconnu</t>
         </is>
-      </c>
-      <c r="D26">
-        <v>3</v>
-      </c>
-      <c r="E26">
-        <v>75</v>
       </c>
     </row>
     <row r="27">
@@ -964,7 +922,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -973,10 +931,10 @@
         </is>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="E27">
-        <v>25</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -992,37 +950,31 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D28">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E28">
-        <v>18.4</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6-10 ans</t>
+          <t>11-14 ans</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>62</v>
-      </c>
-      <c r="E29">
-        <v>81.59999999999999</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1038,14 +990,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="E30">
-        <v>2.9</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1061,14 +1013,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D31">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="E31">
-        <v>82.40000000000001</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="32">
@@ -1079,19 +1031,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11-14 ans</t>
+          <t>15-17 ans</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E32">
-        <v>14.7</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="33">
@@ -1107,14 +1059,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D33">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E33">
-        <v>65.7</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="34">
@@ -1125,19 +1077,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15-17 ans</t>
+          <t>18-25 ans</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D34">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E34">
-        <v>34.3</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35">
@@ -1153,14 +1105,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D35">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="E35">
-        <v>75</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="36">
@@ -1176,14 +1128,8 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D36">
-        <v>10</v>
-      </c>
-      <c r="E36">
-        <v>17.9</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -1194,19 +1140,13 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D37">
-        <v>4</v>
-      </c>
-      <c r="E37">
-        <v>7.1</v>
+          <t>Primaire</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -1222,14 +1162,8 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D38">
-        <v>2</v>
-      </c>
-      <c r="E38">
-        <v>33.3</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -1240,7 +1174,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1249,10 +1183,10 @@
         </is>
       </c>
       <c r="D39">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="E39">
-        <v>66.7</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1268,7 +1202,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D40">
@@ -1281,24 +1215,18 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6-10 ans</t>
+          <t>11-14 ans</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D41">
-        <v>35</v>
-      </c>
-      <c r="E41">
-        <v>81.40000000000001</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -1314,14 +1242,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="E42">
-        <v>1.6</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="43">
@@ -1337,14 +1265,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D43">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="E43">
-        <v>82.3</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="44">
@@ -1360,14 +1288,8 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D44">
-        <v>9</v>
-      </c>
-      <c r="E44">
-        <v>14.5</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -1378,19 +1300,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11-14 ans</t>
+          <t>15-17 ans</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E45">
-        <v>1.6</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="46">
@@ -1406,14 +1328,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D46">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E46">
-        <v>58.8</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="47">
@@ -1429,14 +1351,8 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D47">
-        <v>13</v>
-      </c>
-      <c r="E47">
-        <v>38.2</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -1447,19 +1363,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15-17 ans</t>
+          <t>18-25 ans</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E48">
-        <v>2.9</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="49">
@@ -1475,14 +1391,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D49">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E49">
-        <v>46.9</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="50">
@@ -1498,14 +1414,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D50">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E50">
-        <v>39.1</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="51">
@@ -1516,19 +1432,13 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D51">
-        <v>6</v>
-      </c>
-      <c r="E51">
-        <v>9.4</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -1539,19 +1449,13 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D52">
-        <v>3</v>
-      </c>
-      <c r="E52">
-        <v>4.7</v>
+          <t>Primaire</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -1567,14 +1471,8 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D53">
-        <v>5</v>
-      </c>
-      <c r="E53">
-        <v>71.40000000000001</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -1585,19 +1483,13 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D54">
-        <v>2</v>
-      </c>
-      <c r="E54">
-        <v>28.6</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -1613,14 +1505,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D55">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="E55">
-        <v>12.3</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="56">
@@ -1636,14 +1528,8 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D56">
-        <v>69</v>
-      </c>
-      <c r="E56">
-        <v>85.2</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -1659,14 +1545,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E57">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="58">
@@ -1685,12 +1571,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="D58">
-        <v>4</v>
-      </c>
-      <c r="E58">
-        <v>1.8</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1751,14 +1631,8 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D61">
-        <v>1</v>
-      </c>
-      <c r="E61">
-        <v>0.5</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -1820,7 +1694,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D64">
@@ -1889,14 +1763,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D67">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E67">
-        <v>12</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="68">
@@ -1907,19 +1781,13 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D68">
-        <v>9</v>
-      </c>
-      <c r="E68">
-        <v>3.2</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -1935,14 +1803,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D69">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E69">
-        <v>55.6</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="70">
@@ -1958,14 +1826,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D70">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E70">
-        <v>44.4</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="71">
@@ -1984,12 +1852,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="D71">
-        <v>39</v>
-      </c>
-      <c r="E71">
-        <v>14.1</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2030,11 +1892,28 @@
           <t>Secondaire 1er cycle</t>
         </is>
       </c>
-      <c r="D73">
-        <v>2</v>
-      </c>
-      <c r="E73">
-        <v>0.7</v>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>6-10 ans</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+      <c r="D74">
+        <v>35</v>
+      </c>
+      <c r="E74">
+        <v>12.6</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_class_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_class_marovoay_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -407,7 +407,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -430,7 +430,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -447,7 +447,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -470,7 +470,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -510,7 +510,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -556,7 +556,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -648,7 +648,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -694,7 +694,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -717,7 +717,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -734,7 +734,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -780,7 +780,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -797,7 +797,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -820,7 +820,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -866,7 +866,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -900,7 +900,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -917,7 +917,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -940,7 +940,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -980,7 +980,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1026,7 +1026,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1049,7 +1049,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1072,7 +1072,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1095,7 +1095,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1118,7 +1118,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1152,7 +1152,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1169,7 +1169,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1192,7 +1192,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1215,7 +1215,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1232,7 +1232,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1255,7 +1255,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1278,7 +1278,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1318,7 +1318,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1341,7 +1341,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1404,7 +1404,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1461,7 +1461,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1478,7 +1478,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1495,7 +1495,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1518,7 +1518,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1535,7 +1535,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1558,7 +1558,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1575,7 +1575,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1598,7 +1598,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1638,7 +1638,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1684,7 +1684,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1730,7 +1730,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1753,7 +1753,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1776,7 +1776,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1793,7 +1793,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1816,7 +1816,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1839,7 +1839,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1856,7 +1856,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1879,7 +1879,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1896,7 +1896,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
